--- a/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
+++ b/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#PCB#\PRJ_Dongle01\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{076221BF-07D0-42C6-8076-E49E953EC2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9784AA37-CFC5-48D3-B39C-806FF0388847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{B155109C-8E9C-4239-9510-B517567E199B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{F5F5A496-EB91-47FB-861B-B779DBC0FB96}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials Tech-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -870,7 +870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6238BD-B82E-4B48-B618-91522F473341}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC71F2B0-56B4-47C1-8A3A-2797AE0B775D}">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
